--- a/loan_free.xlsx
+++ b/loan_free.xlsx
@@ -59,16 +59,16 @@
     <t>30/7/2026</t>
   </si>
   <si>
-    <t>30/12/2026</t>
-  </si>
-  <si>
     <t>25/8/2026</t>
   </si>
   <si>
-    <t>25/01/2027</t>
-  </si>
-  <si>
     <t>Baqqalaa Tolasaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           25/1/2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        30/12/2026</t>
   </si>
 </sst>
 </file>
@@ -104,9 +104,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,8 +444,8 @@
       <c r="C3">
         <v>10000</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
@@ -453,12 +456,12 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>10000</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
@@ -484,7 +487,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
         <v>46304</v>
@@ -501,5 +504,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/loan_free.xlsx
+++ b/loan_free.xlsx
@@ -106,9 +106,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,7 +396,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -404,7 +406,7 @@
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -421,13 +423,13 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>46059</v>
       </c>
       <c r="C2">
         <v>10000</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>46064</v>
       </c>
       <c r="E2" t="s">
@@ -438,7 +440,7 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -455,7 +457,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -472,13 +474,13 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>46151</v>
       </c>
       <c r="C5">
         <v>10000</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>46509</v>
       </c>
       <c r="E5" t="s">
@@ -489,13 +491,13 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>46304</v>
       </c>
       <c r="C6">
         <v>7500</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>46307</v>
       </c>
       <c r="E6" t="s">

--- a/loan_free.xlsx
+++ b/loan_free.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>loan_amount</t>
   </si>
@@ -56,19 +56,13 @@
     <t>Gizahu Hayiluu</t>
   </si>
   <si>
-    <t>30/7/2026</t>
-  </si>
-  <si>
-    <t>25/8/2026</t>
-  </si>
-  <si>
     <t>Baqqalaa Tolasaa</t>
   </si>
   <si>
-    <t xml:space="preserve">           25/1/2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        30/12/2026</t>
+    <t xml:space="preserve">        12/30/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           1/25/2027</t>
   </si>
 </sst>
 </file>
@@ -424,13 +418,13 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="C2">
         <v>10000</v>
       </c>
       <c r="D2" s="2">
-        <v>46064</v>
+        <v>46328</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
@@ -440,14 +434,14 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
+      <c r="B3" s="2">
+        <v>46233</v>
       </c>
       <c r="C3">
         <v>10000</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
@@ -457,14 +451,14 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
+      <c r="B4" s="2">
+        <v>46259</v>
       </c>
       <c r="C4">
         <v>10000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
@@ -475,13 +469,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>46151</v>
+        <v>46270</v>
       </c>
       <c r="C5">
         <v>10000</v>
       </c>
       <c r="D5" s="2">
-        <v>46509</v>
+        <v>46423</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
@@ -489,16 +483,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>46304</v>
+        <v>46275</v>
       </c>
       <c r="C6">
         <v>7500</v>
       </c>
       <c r="D6" s="2">
-        <v>46307</v>
+        <v>46366</v>
       </c>
       <c r="E6" t="s">
         <v>4</v>
